--- a/pidsg25-04_historical.xlsx
+++ b/pidsg25-04_historical.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/forecast25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/pricesaa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1618C81-ECF2-694A-8297-1D29DD756E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C9A8F1-8A8A-B247-8386-33C20316A0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15220" yWindow="5080" windowWidth="16380" windowHeight="12220" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="1800" windowWidth="16380" windowHeight="12220" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="p1normal" sheetId="1" r:id="rId1"/>
